--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_003/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -445,11 +450,6 @@
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>CFD prediction of inlet pressure recovery and swirl distortion for eVTOL S-duct at AoA 0–12°, M=0.25–0.5</t>
+          <t>Predict inlet pressure recovery and swirl distortion at AIP for eVTOL S-duct over AoA 0–12°, M=0.25–0.5</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS CFD (STAR-CCM+ 2021.3, SST k-ω) used to predict AIP pressure recovery and DC60/DC90 swirl distortion indices for an eVTOL demonstrator engine intake S-duct across cruise and off-design yaw/AoA conditions. Model outputs support airframe–propulsor integration clearance and fan operability guard band decisions at preliminary design gate.</t>
+          <t>Steady RANS CFD model of a 22° centerline-bend S-duct inlet used to predict AIP pressure recovery and DC60/DC90 swirl distortion indices for airframe–propulsor integration and fan operability guard-band decisions at preliminary design gate. Intended operating envelope: AoA 0–12°, Mach 0.25–0.5, ReD ≈ 2.7e6, clean configuration only.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1369,9 +1369,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (S-Duct UAV Inlet CFD Credibility Briefing Rev B, Aero Systems CFD Team, 2025)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Inlet pressure recovery predicted within ±2% absolute and distortion indices (DC60/DC90) within ±10% of tunnel data across AoA 0–12°, M=0.25–0.5, ReD ≈ 2.7e6; results must support pre-PDR airframe–propulsor integration and fan operability guard band decisions.</t>
+          <t>CFD model must predict AIP pressure recovery within ±2% absolute and swirl distortion indices (DC60/DC90) within ±10% of tunnel data across AoA 0–12°, M=0.25–0.5</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>STAR-CCM+ Steady RANS SST k-ω CFD Model</t>
+          <t>STAR-CCM+ Steady RANS SST k-ω Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady RANS model with SST k-ω (low-Re correction), compressibility, second-order convection/pressure schemes, coupled pseudo-transient solver; poly-hexcore grids (2.1M–8.7M cells); primary tool for AIP pressure recovery and swirl distortion prediction.</t>
+          <t>Steady compressible RANS with SST k-ω (low-Re correction), poly-hexcore mesh, second-order convection and pressure schemes, coupled pseudo-transient solver; primary model for AIP QoI prediction</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Realizable k-ε with enhanced wall treatment, used for high-yaw (AoA ≥10°) sensitivity and turbulence model uncertainty assessment; shows ~13% relative DC60 reduction vs SST at AoA=10°.</t>
+          <t>Realizable k-ε with enhanced wall treatment, used for high-yaw (AoA ≥10°) cases to mitigate solver instability; shows 13% relative DC60 difference vs SST at AoA=10°</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0.4-m rig wind tunnel data including PIV planes at x/D=−0.2, 0.0, +0.8; five-hole probe rake at AIP; calibrated venturi mass flow; AoA 0–8°, M=0.25–0.5; turbulence intensity 3.3% measured; post-campaign venturi drift of 1.6% discovered.</t>
+          <t>0.4-m rig PIV planes and five-hole probe rake at AIP; calibrated venturi mass flow; four AoA points covering 0–8°; 3.3% measured inlet turbulence intensity; post-campaign venturi drift of 1.6% partially corrected</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>CFD Case Files and Mesh Repository</t>
+          <t>Mesh Convergence Study Dataset</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Git LFS repository (tags v0.7.3–v0.8.1) containing Pointwise V18.4 meshes, STAR-CCM+ journal files, and Python post-processing scripts; CI pipeline on Cluster-B (CentOS 8); exceptions noted for corrupted Fine grid at AoA=12° and missing AIP probe mask file.</t>
+          <t>Coarse (2.1M), Medium (5.3M), Fine (8.7M) poly-hexcore grids; GCI on AIP pressure recovery = 0.9% at M=0.35, AoA=0°; swirl RMS change &lt;0.5° between Medium and Fine</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>AIP Pressure Recovery Comparison (AoA 0–8°)</t>
+          <t>AIP Pressure Recovery Comparison to Tunnel Data (AoA 0–8°)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>CFD-predicted AIP pressure recovery compared against five-hole probe rake measurements from AeroLabs tunnel campaign at four operating points across AoA=0–8°, M=0.25–0.5.</t>
+          <t>Steady RANS SST predictions of AIP pressure recovery compared to five-hole probe rake measurements from AeroLabs tunnel campaign at four operating points (AoA=0°–8°, M=0.25–0.5)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>AeroLabs five-hole probe rake measurements (July–Aug 2025)</t>
+          <t>AeroLabs five-hole probe rake measurements, calibrated venturi mass flow</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Reported ±1.1% recovery band from 32-sample Latin hypercube (inlet TI and mass flow varied); venturi corrected for last two AoA points only.</t>
+          <t>Reported ±1.1% recovery band from 32-sample Latin hypercube (TI and mass flow inputs only); post-campaign venturi drift correction of 1.6% partially applied</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Mean absolute error 2.4% (AoA 0–8°); worst case 3.8% high at AoA=8°, M=0.5; 1.1% low at AoA=0°, M=0.25</t>
+          <t>Mean absolute error 2.4% (AoA 0–8°); worst point +3.8% (AoA=8°, M=0.5); best point −1.1% (AoA=0°, M=0.25)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>DC60 Swirl Distortion Comparison</t>
+          <t>DC60 Swirl Distortion Comparison to Tunnel Data</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>CFD-predicted DC60 distortion index compared against five-hole probe rake data at AIP; qualitative swirl pattern (clockwise bias) assessed in addition to quantitative index.</t>
+          <t>CFD-predicted DC60 distortion index at AIP compared to tunnel five-hole probe rake across AoA=0–8° range</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>AeroLabs five-hole probe rake AIP measurements</t>
+          <t>AeroLabs five-hole probe rake DC60 measurements</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2085,14 +2085,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Turbulence model sensitivity only (SST vs realizable k-ε produces ~13% relative DC60 difference at AoA=10° vs ~5% in tunnel)</t>
-        </is>
-      </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>DC60 within 7–10% of experiment for AoA=0–8°; model-form sensitivity ~13% at AoA=10°</t>
+          <t>DC60 within 7–10% of experiment; qualitative swirl pattern (clockwise bias) captured</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2114,12 +2109,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study (coarse 2.1M, medium 5.3M, fine 8.7M cells) assessing discretization error in AIP pressure recovery at M=0.35, AoA=0°.</t>
+          <t>Three-level structured refinement study on AIP pressure recovery at M=0.35, AoA=0° using Coarse (2.1M), Medium (5.3M), and Fine (8.7M) grids; Richardson extrapolation performed; non-monotone behavior noted at M=0.5, AoA=8°</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / zero-mesh extrapolation</t>
+          <t>Richardson-extrapolated zero-mesh value</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2129,24 +2124,24 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI) computed for nominally monotone convergence; non-monotone behavior noted at M=0.5, AoA=8°.</t>
+          <t>Grid Convergence Index (GCI)</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>GCI on recovery = 0.9%; coarse-to-medium change +1.1%; medium-to-fine +0.3%; swirl RMS change &lt;0.5 deg</t>
+          <t>GCI = 0.9% on pressure recovery; Coarse→Medium change +1.1%, Medium→Fine +0.3%; non-monotone patch −0.4% at M=0.5 AoA=8°</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Numerical Code Verification (MMS and Benchmark)</t>
+          <t>Numerical Code Verification — Manufactured Solution and Benchmark</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2156,12 +2151,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Manufactured solution test on structured scalar advection box and laminar lid-driven cavity (Re=1000) benchmark against Ghia et al. to verify code correctness.</t>
+          <t>Scalar advection manufactured solution on structured box and laminar lid-driven cavity (Re=1000) compared to Ghia et al. to verify code order of accuracy</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Analytical manufactured solution; Ghia et al. benchmark data</t>
+          <t>Analytical manufactured solution (order of accuracy); Ghia et al. benchmark centerline velocities</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2171,7 +2166,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Observed order 1.98 (velocity), 1.91 (pressure) vs nominal 2nd-order; lid-driven cavity centerline velocities within 0.8% of Ghia et al.</t>
+          <t>Observed order 1.98 (velocity), 1.91 (pressure); lid-driven cavity within 0.8% of Ghia et al.</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2183,7 +2178,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Monitoring</t>
+          <t>Turbulence Model Sensitivity at High AoA</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2193,12 +2188,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Residual drop, mass imbalance, and area-averaged recovery monitor stability assessed across production runs; first-order fallback documented for high-yaw cases.</t>
+          <t>Comparison of SST k-ω vs realizable k-ε predictions of DC60 at AoA=10° to assess model-form uncertainty</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Internal convergence criteria</t>
+          <t>Tunnel DC60 measurement at AoA=10°</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2208,12 +2203,12 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Residuals dropped 3–4 orders; mass imbalance &lt;0.1%; recovery stable within 0.2% over 2000 iterations; first-order fallback used on some high-yaw cases (residuals recovered 2 orders, monitors moved &lt;0.5%)</t>
+          <t>SST to k-ε DC60 difference ~13% relative; tunnel DC60 drop ~5%</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2357,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented version control, patch management, and regression evidence</t>
+          <t>Commercial solver with documented verification and regression testing; version control for case files</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2021.3 (commercial, widely certified) used as primary solver. Patch HF2 applied mid-campaign for memory leak; no regression found on baseline case. Runs managed via CI pipeline on Cluster-B with Git LFS version tracking (tags v0.7.3–v0.8.1). Pointwise V18.4 used for meshing. No formal ISO certification documentation cited, but commercial pedigree and patch regression provide adequate SQA evidence for pre-PDR level. Note: template version mismatch (v18.4.5 vs v18.4.6) after storage crash is a minor gap.</t>
+          <t>STAR-CCM+ 2021.3 (commercial solver) with patch HF2 applied mid-campaign for memory leak; no regression found on baseline case after patch. Case files, meshes, and scripts tracked in Git LFS with tags v0.7.3–v0.8.1. CI pipeline used for run generation on Cluster-B. Peer review held 2025-08-22. Gaps: several high-yaw cases restarted by new analyst with first-order scheme enabled without supervisor sign-off; those cases flagged for re-run.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2396,12 +2391,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Observed numerical order close to formal order; benchmark agreement within acceptable tolerance</t>
+          <t>Observed order of accuracy consistent with nominal scheme order; benchmark agreement within accepted tolerance</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Manufactured solution on structured scalar advection box yielded observed order 1.98 (velocity) and 1.91 (pressure), consistent with nominal second-order scheme. Laminar lid-driven cavity at Re=1000 matched Ghia et al. centerline velocities within 0.8%. Both are standard code verification activities providing good evidence. Verification limited to simplified geometries; no MMS on the full 3-D S-duct configuration.</t>
+          <t>Manufactured solution (scalar advection) on structured box yields observed order 1.98 (velocity) and 1.91 (pressure), consistent with nominal second-order schemes. Laminar lid-driven cavity at Re=1000 matches Ghia et al. centerline velocities within 0.8%. Both verification activities are documented in run sheets.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2426,16 +2421,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>GCI &lt; 1% on primary QoI; monotone convergence demonstrated</t>
+          <t>Monotone mesh convergence with GCI &lt;1% for primary QoI across the full operating envelope</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level mesh study (2.1M, 5.3M, 8.7M cells) performed at M=0.35, AoA=0°. GCI on AIP pressure recovery = 0.9% (nominally monotone). Swirl RMS changed &lt;0.5 deg. However, non-monotone behavior observed at M=0.5, AoA=8° (fine grid 0.4% lower than medium). y+ excursions (6–8) in separated corner at AoA≥10° reduce confidence at off-design. GCI not yet documented at M=0.5 (open action). Adequate for AoA≤8° primary condition, with noted gaps at high AoA and high Mach.</t>
+          <t>Three-level refinement study (2.1M, 5.3M, 8.7M cells) performed at M=0.35, AoA=0°; GCI = 0.9% on pressure recovery; swirl RMS change &lt;0.5°. However, non-monotone behavior observed at M=0.5, AoA=8° (Fine predicts −0.4% lower than Medium). y+ exceeds 6–8 in separated corner bubble for AoA ≥10° on Medium grid. Rebuilt AoA=12° mesh after storage crash shows 3.7% recovery discrepancy vs archived Medium. GCI at M=0.5 and high AoA not formally documented.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2464,12 +2459,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals drop ≥3 orders; mass imbalance &lt;0.1%; monitors stable; consistent scheme order throughout</t>
+          <t>Residuals converged ≥3 orders; mass imbalance &lt;0.1%; monitors stable; consistent scheme usage throughout production runs</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>For most production runs: residuals dropped 3–4 orders, mass imbalance &lt;0.1%, area-averaged recovery stable within 0.2% over 2000 iterations — satisfactory. However, a significant issue exists: several high-yaw cases were restarted by the new analyst with first-order scheme to pass stalls; final 400 iterations on multiple high-yaw cases used first-order upwind after divergence events. While monitors moved &lt;0.5%, mixing first- and second-order within a run is a solver integrity concern flagged for re-run. This lowers confidence for the high-AoA regime specifically.</t>
+          <t>Residuals dropped 3–4 orders; mass imbalance &lt;0.1%; area-averaged recovery stable within 0.2% over last 2k iterations. However, final 400 iterations on several high-yaw cases were completed with first-order upwind after divergence events; scheme inconsistency is an open concern. New analyst re-ran high-yaw cases with first-order enabled; flagged for re-run but not yet resolved.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2498,12 +2493,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent peer review covering boundary condition setup, mesh quality, and post-processing; all findings closed</t>
+          <t>Independent peer review completed; boundary conditions documented and consistent; mesh quality verified; post-processing traceability confirmed</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Peer check held 2025-08-22; two minor findings closed (AIP plane alignment, TI consistency). Lead analyst has 12 years of inlet CFD experience. However, multiple use errors are documented: (1) new team member with no prior S-duct experience prepared AoA=10–12° decks and used first-order fallback without authorization; (2) AoA=12–15° screening runs used inverted BC strategy (mass flow inlet, static pressure outlet) differing from production; (3) early shakedown used velocity inlet (5% TI) before switching to total pressure inlet; (4) AIP probe mask file missing from repository and reconstructed from JPEG. These are material use-error indicators reducing confidence.</t>
+          <t>Peer check held 2025-08-22; two minor findings closed (AIP plane alignment, TI consistency). Git LFS versioning provides case traceability. However, several gaps exist: BC strategy changed between shakedown (velocity inlet, 5% TI) and production (total pressure inlet); AoA=12–15° screens used an inverted BC pairing (mass flow inlet, static pressure outlet); AIP probe mask file missing from repository and reconstructed from JPEG; new analyst prepared AoA=10–12° decks without prior S-duct experience. Production TI (5%) does not match tunnel measurement (3.3%).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2532,12 +2527,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified; known limitations documented; model-form sensitivity quantified</t>
+          <t>Turbulence model selection justified; known model-form limitations documented; physics assumptions appropriate for operating envelope</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>SST k-ω with low-Re correction is a well-established choice for internal flows with adverse pressure gradients; compressibility and adiabatic walls are reasonable for the regime. Fully turbulent assumption documented (no transition model). Realizable k-ε alternative run at high yaw provides sensitivity insight. Key limitation: at AoA=10°, SST vs realizable k-ε produces ~13% relative DC60 difference while tunnel shows only ~5% drop, indicating significant model-form uncertainty at high AoA. Corner separation fidelity is explicitly noted as uncertain. Surface roughness not modeled despite measured Ra variability (1.4–3.1 µm). Steady RANS assumption may be inappropriate for highly separated regimes above AoA=10°.</t>
+          <t>SST k-ω selected as baseline with justification (low-Re correction, compressibility). Model limitations documented: fully turbulent (no transition model), no acoustic–fan coupling, no rotating stall, no roughness model despite Ra 1.4–3.1 µm coupon measurements. Turbulence model sensitivity at AoA=10° shows 13% DC60 difference between SST and realizable k-ε vs 5% in tunnel, indicating significant model-form uncertainty at high AoA. Corner separation fidelity explicitly flagged as uncertain above AoA=10°.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2566,12 +2561,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions from measurement; material properties documented; geometry from CAD; input uncertainties characterized</t>
+          <t>Inlet conditions and geometry matched to test; input uncertainty characterized; material properties traceable</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Geometry from CAD Rev_31 (22° bend, 9% contraction); surface roughness not modeled despite coupon measurements (1.4–3.1 µm). Thermophysical properties from Sutherland's law and ideal gas — standard and documented. Inflow turbulence mismatch: production runs used TI=5%, integral length 0.1 m, while tunnel measured TI=3.3% and 0.07 m — a known and unresolved input discrepancy. Geometry simplifications (fastener heads, paint step, fillet radius compressed) are documented. Re-run with TI=3.3% is an open action. LHS uncertainty sampling covered only 5 inputs with roughness held fixed.</t>
+          <t>Geometry matched within 0.3 mm; Sutherland's law for air viscosity; ideal gas density. Inlet turbulence intensity used in production (5%) does not match tunnel measurement (3.3%); integral length scale 0.1 m vs measured 0.07 m. Wall roughness not modeled despite measured Ra 1.4–3.1 µm on coupons. Fastener heads and lip paint step omitted. UQ sensitivity study planned for five inputs but executed only for two (TI, mass flow) at 32 LHS samples; roughness held constant at smooth. Input mismatch flagged as open action.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2600,12 +2595,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article production-representative; sufficient comparison points; geometry characterization documented</t>
+          <t>Adequate number of test conditions; production-representative geometry; documented specimen characterization</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Single 0.4-m rig test article used at AeroLabs; geometry match documented within 0.3 mm. Bleed and lip conditions matched. No information on number of repeat articles, geometric variability characterization, or production-representativeness beyond dimensional match. Four nominal comparison points cited (AoA=0–8° mean). AIP probe mask file is missing from repository and was reconstructed from a JPEG — reducing traceability confidence. Limited statistical characterization of test article population.</t>
+          <t>Four AoA operating points (0°–8°) measured in tunnel; PIV at three axial planes; five-hole probe rake at AIP; calibrated venturi for mass flow. Only one physical rig configuration; no replicate runs or statistical sample size justification provided. Tunnel article geometry matched within 0.3 mm. Test article cleaned before runs (roughness not characterized on rig). AoA=10–12° range not covered by formal tunnel campaign.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2634,12 +2629,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instruments; measurement uncertainty quantified; test conditions controlled and documented</t>
+          <t>Calibrated instruments; controlled environment; measurement uncertainty quantified; test standards followed</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>PIV planes, five-hole probe rake, and calibrated venturi used for measurements. Inlet turbulence measured at 3.3% via hot-wire rake. However, a significant data quality issue exists: post-campaign recalibration of the venturi revealed 1.6% drift, and mass flow correction was applied only to the last two AoA points. This is a systematic measurement error affecting at least half the validation dataset. No measurement uncertainty bounds formally quoted for recovery or DC60 test values. Environment control (matte composite, cleaned article) is documented.</t>
+          <t>Inlet turbulence measured at 3.3% via hot-wire rake. Mass flow via calibrated venturi, but 1.6% drift discovered post-campaign; correction applied only to last two AoA points, not consistently to all data. Measurement uncertainty for five-hole probe and PIV not explicitly stated in briefing. No reference to ASTM/ISO test standards. AIP probe mask file missing from repository; reconstructed from JPEG, introducing traceability gap.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2668,12 +2663,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD boundary conditions match experimental conditions within measurement uncertainty; mismatches quantified</t>
+          <t>CFD boundary conditions demonstrably match experimental conditions; input discrepancies quantified and bounded</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Geometry alignment within 0.3 mm and bleed/lip conditions matched. However, inlet turbulence intensity mismatch (CFD: 5.0%, test: 3.3%) and integral length scale mismatch (0.1 m vs 0.07 m) are acknowledged discrepancies that affect DC60 predictions nonlinearly above TI=4%. Mass flow boundary condition inconsistency (venturi drift uncorrected for two early points) further reduces equivalency. BC strategy changed between shakedown and production runs (velocity inlet vs total pressure inlet). Corrections are open actions, not yet implemented consistently.</t>
+          <t>Geometry alignment confirmed within 0.3 mm; inlet total pressure and temperature matched; bleed and lip conditions matched. However, CFD uses TI=5% and L=0.1 m while tunnel measured TI=3.3% and L=0.07 m — discrepancy not corrected in production decks (flagged as open action). Venturi drift correction inconsistently applied across test points. BC strategy differences between shakedown and production runs and between AoA regimes not fully reconciled.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2702,12 +2697,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative error metrics reported for all primary QoIs; uncertainty bands on predictions and measurements; comparison across full operating envelope</t>
+          <t>Quantitative error metrics for all primary QoI across full operating envelope; uncertainty bands on comparison; all data points included</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative recovery comparison reported: mean 2.4% absolute error (AoA=0–8°), exceeding the ±2% program target; worst case 3.8% at AoA=8°, M=0.5. DC60 within 7–10% (within ±10% target for most points). Swirl pattern qualitatively correct. However: (1) "within ±3%" in draft abstract achieved only by excluding the worst-case point and restricting M range; (2) measurement uncertainty bands not formally quantified on test side; (3) no GCI bars plotted alongside comparison; (4) AoA&gt;8° comparison not formally reported; (5) venturi correction inconsistency affects baseline data quality. LHS-derived ±1.1% recovery prediction band reported for M=0.35 only.</t>
+          <t>Pressure recovery compared quantitatively: mean error 2.4% for AoA=0–8° (exceeds ±2% program target); worst point +3.8% at AoA=8°, M=0.5. DC60 within 7–10% (within ±10% target for most points). Swirl pattern qualitatively captured. However: "within ±3%" claim in draft abstract excludes AoA=8° high-Mach outlier and is limited to M=0.25–0.35 — selective reporting. UQ bands cover only two inputs. No formal statistical validation metric (e.g., MAPE, u-pooled). AoA=10–12° range has no formal comparison to data.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2732,16 +2727,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (recovery, DC60/DC90) directly measure the safety/performance concern and are measurable both computationally and experimentally</t>
+          <t>QoI directly measures the performance/safety concern and is measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>AIP pressure recovery and DC60/DC90 swirl distortion are the standard, directly relevant metrics for fan operability and airframe–propulsor integration decisions. Both are defined identically in CFD post-processing (area-averaged AIP pressure, circumferential distortion index) and in the experimental rake measurements. QoIs are well-aligned with the decision (operability guard bands, integration clearance). DC90 is mentioned as a target metric but results reported primarily for DC60; minor gap.</t>
+          <t>AIP pressure recovery and DC60/DC90 distortion indices are the standard industry QoI for inlet–fan compatibility and operability margin assessment. Both are directly computed from CFD (area-averaged static and total pressure at AIP plane) and directly measured by five-hole probe rake in tunnel. These QoI feed directly into the fan operability guard-band decision and airframe–propulsor integration clearance. QoI selection is well-justified and unambiguous.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2770,12 +2765,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation covers the full COU envelope (AoA 0–12°, M=0.25–0.5); same geometry, same physics regime; gaps documented</t>
+          <t>Validation covers the full COU envelope (AoA 0–12°, M=0.25–0.5); same geometry; same flow regime; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation campaign covers AoA=0–8° and M=0.25–0.5 (partial). The upper half of the COU envelope (AoA=8–12°) has no formal validation data — only engineering screens with different BC strategies and mesh concerns. Geometry is the same CAD revision. Reynolds number and Mach range partially covered. The 0.4-m rig is a subscale facility; Reynolds number scaling not explicitly discussed. Fully turbulent assumption and no acoustic/rotating stall coupling acknowledged as limitations. The report explicitly restricts confidence to AoA≤8° for design use, leaving the AoA=8–12° COU range without validated predictions.</t>
+          <t>Validation tunnel campaign covers AoA=0–8° only; AoA=8–12° portion of the stated COU has no formal validation data. Mach range partially covered (M=0.25–0.5 stated; tunnel data primarily M=0.25–0.35 per draft abstract qualification). Geometry is production-representative within 0.3 mm. Flow regime is subsonic compressible RANS — consistent with COU. Gaps at high AoA and high Mach are explicitly acknowledged; stretch cases at AoA=15–18° used different BC strategy and are informal. Applicability to full COU is limited without additional validation data above AoA=8°.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2960,7 +2955,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The model is accepted with conditions for concept-ranking and pre-PDR trade studies at AoA≤8° only, consistent with the analyst team's own go/no-go recommendation. For this sub-envelope, AIP recovery error (2.4% mean, 3.8% worst case) is close to but slightly exceeds the ±2% program target; DC60 is within the ±10% target; mesh GCI (0.9%) is acceptable; code verification benchmarks are satisfactory; and the peer review is on record. Acceptance is conditional on the following open actions being closed before committing design margins at AoA&gt;8°: (1) re-run AoA=8–12° cases with consistent SST second-order scheme and corrected TI=3.3%; (2) recover and re-tag exact Fine mesh settings post-crash and document GCI at M=0.5 with uncertainty bars; (3) apply venturi correction consistently across all validation points and recover AIP probe mask file in repository; (4) expand uncertainty sampling to ≥128 LHS samples or polynomial chaos and include roughness sweep; (5) resolve and document the first-order fallback usage by the new analyst. Use of results above AoA=8° for margin commitment is not authorized until these actions are closed.</t>
+          <t>The model is accepted with conditions for the restricted sub-envelope AoA ≤8°, M=0.25–0.35, where CFD pressure recovery is within 2.4% (marginally exceeding the ±2% program target at the worst point) and DC60 is within 7–10% of tunnel data (within the ±10% target). The briefing's own go/no-go recommendation supports use for concept ranking at AoA ≤8°. Acceptance is conditional on: (1) re-running AoA=8–12° cases with consistent SST, second-order schemes, and corrected TI=3.3%; (2) recovering and re-tagging the Fine mesh after the storage crash and documenting GCI at M=0.5; (3) expanding UQ sampling to ≥128 LHS samples and including roughness sweep; (4) consistently applying the venturi drift correction across all test points and publishing the AIP probe mask file; (5) not using current results for design margin commitments above AoA=8°. Multiple open credibility gaps (input mismatch, partial venturi correction, BC inconsistencies, missing traceability artifacts, solver scheme swaps) must be resolved before extension to the full AoA 0–12° COU envelope.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
